--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487950_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487950_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0118</v>
+        <v>4.9975</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5074</v>
+        <v>1.8754</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5044</v>
+        <v>3.1221</v>
       </c>
       <c r="G2" t="n">
         <v>3.3446</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7979</v>
+        <v>-0.8122</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9139</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.884</v>
+        <v>-0.2663</v>
       </c>
       <c r="V2" t="n">
         <v>0.4828</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6119</v>
+        <v>3.1698</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0695</v>
+        <v>1.2732</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5424</v>
+        <v>1.8966</v>
       </c>
       <c r="G3" t="n">
         <v>1.1081</v>
@@ -688,13 +688,13 @@
         <v>1.9822</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.082</v>
+        <v>-0.5241</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6753</v>
+        <v>-0.4716</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5933</v>
+        <v>-0.0525</v>
       </c>
       <c r="V3" t="n">
         <v>0.6036</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2406</v>
+        <v>1.9089</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8387</v>
+        <v>0.7598</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4019</v>
+        <v>1.1491</v>
       </c>
       <c r="G4" t="n">
         <v>0.132</v>
@@ -766,13 +766,13 @@
         <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4958</v>
+        <v>0.1642</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.121</v>
+        <v>-0.1999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6168</v>
+        <v>0.3641</v>
       </c>
       <c r="V4" t="n">
         <v>0.8198</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>E. TRUJILLO MARIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0492</v>
+        <v>1.4856</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4915</v>
+        <v>-1.5283</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4423</v>
+        <v>3.0139</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3347</v>
+        <v>3.6292</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3342</v>
+        <v>2.8047</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0006</v>
+        <v>0.8245</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7572</v>
+        <v>1.5045</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7131</v>
+        <v>2.1797</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0441</v>
+        <v>-0.6752</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5775</v>
+        <v>2.1247</v>
       </c>
       <c r="N5" t="n">
-        <v>0.621</v>
+        <v>0.625</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9565</v>
+        <v>1.4998</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5858</v>
+        <v>-1.784</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1905</v>
+        <v>-0.4351</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7343</v>
+        <v>-0.4716</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9248</v>
+        <v>0.0365</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.6808</v>
+        <v>0.0755</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4033</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.6808</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. TRUJILLO MARIN</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7078</v>
+        <v>0.3247</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8568</v>
+        <v>0.7389</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5647</v>
+        <v>-0.4142</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6292</v>
+        <v>2.3347</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8047</v>
+        <v>1.3342</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8245</v>
+        <v>1.0006</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5045</v>
+        <v>0.7572</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1797</v>
+        <v>0.7131</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6752</v>
+        <v>0.0441</v>
       </c>
       <c r="M6" t="n">
-        <v>2.1247</v>
+        <v>1.5775</v>
       </c>
       <c r="N6" t="n">
-        <v>0.625</v>
+        <v>0.621</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4998</v>
+        <v>0.9565</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2129</v>
+        <v>-0.915</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8001</v>
+        <v>-0.0183</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4127</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0755</v>
+        <v>-2.6808</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4033</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3278</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7729</v>
+        <v>-0.2854</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0281</v>
+        <v>-1.4563</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2552</v>
+        <v>1.1709</v>
       </c>
       <c r="G7" t="n">
         <v>4.3802</v>
@@ -1000,13 +1000,13 @@
         <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7816</v>
+        <v>-1.2941</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.4045</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8053</v>
+        <v>-0.8895</v>
       </c>
       <c r="V7" t="n">
         <v>-0.7947</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>T. PARRA MENDIVIL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9482</v>
+        <v>-0.9274</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5338</v>
+        <v>-0.583</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4821</v>
+        <v>-0.3443</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7185</v>
+        <v>0.134</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4445</v>
+        <v>0.8056</v>
       </c>
       <c r="I8" t="n">
-        <v>1.274</v>
+        <v>-0.6716</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7495</v>
+        <v>-0.1683</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7093</v>
+        <v>0.3903</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>-0.5586</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.031</v>
+        <v>0.3023</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2648</v>
+        <v>0.4153</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2338</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.1982</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.1893</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>0.67</v>
+        <v>-1.1912</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3107</v>
+        <v>-0.2165</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6407</v>
+        <v>-0.9747</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.1385</v>
+        <v>-0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.8015</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. PARRA MENDIVIL</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1664</v>
+        <v>-1.6215</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9905</v>
+        <v>-0.7328</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1759</v>
+        <v>-0.8887</v>
       </c>
       <c r="G9" t="n">
-        <v>0.134</v>
+        <v>1.1703</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8056</v>
+        <v>-0.4617</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6716</v>
+        <v>1.632</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1683</v>
+        <v>0.662</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3903</v>
+        <v>0.128</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5586</v>
+        <v>0.534</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3023</v>
+        <v>0.5084</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4153</v>
+        <v>-0.5896</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.113</v>
+        <v>1.098</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3964</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4302</v>
+        <v>-1.5253</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.624</v>
+        <v>-0.2055</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8063</v>
+        <v>-1.3198</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2666</v>
+        <v>-0.8701</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2666</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1476</v>
+        <v>-1.866</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2027</v>
+        <v>0.4757</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9448</v>
+        <v>-2.3417</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1703</v>
+        <v>1.7185</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4617</v>
+        <v>0.4445</v>
       </c>
       <c r="I10" t="n">
-        <v>1.632</v>
+        <v>1.274</v>
       </c>
       <c r="J10" t="n">
-        <v>0.662</v>
+        <v>1.7495</v>
       </c>
       <c r="K10" t="n">
-        <v>0.128</v>
+        <v>1.7093</v>
       </c>
       <c r="L10" t="n">
-        <v>0.534</v>
+        <v>0.0402</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5084</v>
+        <v>-0.031</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5896</v>
+        <v>-1.2648</v>
       </c>
       <c r="O10" t="n">
-        <v>1.098</v>
+        <v>1.2338</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1893</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0513</v>
+        <v>-0.2478</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6753</v>
+        <v>0.2525</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.376</v>
+        <v>-0.5003</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8701</v>
+        <v>-3.1385</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8701</v>
+        <v>-2.8015</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3659</v>
+        <v>-2.342</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1399</v>
+        <v>-3.9756</v>
       </c>
       <c r="F11" t="n">
-        <v>1.774</v>
+        <v>1.6336</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3818</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2001</v>
+        <v>-0.1762</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5616</v>
+        <v>-0.3973</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3615</v>
+        <v>0.2211</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.220299999999998</v>
+        <v>4.844199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7771</v>
+        <v>-3.153</v>
       </c>
       <c r="F12" t="n">
-        <v>7.9975</v>
+        <v>7.997299999999999</v>
       </c>
       <c r="G12" t="n">
         <v>17.5698</v>
@@ -1363,25 +1363,25 @@
         <v>7.441899999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>9.120900000000001</v>
+        <v>9.120899999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>9.291900000000002</v>
+        <v>9.2919</v>
       </c>
       <c r="L12" t="n">
         <v>-0.1708999999999998</v>
       </c>
       <c r="M12" t="n">
-        <v>8.4491</v>
+        <v>8.449099999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8362000000000003</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>7.613</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.8755</v>
@@ -1390,13 +1390,13 @@
         <v>13.8756</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.580699999999999</v>
+        <v>-6.956799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.3025</v>
+        <v>-2.6786</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.278199999999999</v>
+        <v>-4.2781</v>
       </c>
       <c r="V12" t="n">
         <v>-5.769</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.042299999999999</v>
+        <v>6.9629</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9292</v>
+        <v>4.9105</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1131</v>
+        <v>2.0524</v>
       </c>
       <c r="G13" t="n">
         <v>2.6021</v>
@@ -1468,13 +1468,13 @@
         <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7396</v>
+        <v>1.6602</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0632</v>
+        <v>1.0445</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6763</v>
+        <v>0.6156</v>
       </c>
       <c r="V13" t="n">
         <v>3.6917</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4447</v>
+        <v>4.2912</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4089</v>
+        <v>2.8995</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0358</v>
+        <v>1.3917</v>
       </c>
       <c r="G14" t="n">
         <v>-1.2682</v>
@@ -1546,13 +1546,13 @@
         <v>1.9822</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8953</v>
+        <v>1.7419</v>
       </c>
       <c r="T14" t="n">
-        <v>1.553</v>
+        <v>1.0437</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3423</v>
+        <v>0.6982</v>
       </c>
       <c r="V14" t="n">
         <v>3.8175</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7091</v>
+        <v>1.941</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0271</v>
+        <v>1.2309</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.7101</v>
       </c>
       <c r="G15" t="n">
         <v>0.6604</v>
@@ -1624,13 +1624,13 @@
         <v>0.5947</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2198</v>
+        <v>0.012</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2386</v>
+        <v>-0.0348</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V15" t="n">
         <v>0.674</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3988</v>
+        <v>0.7595</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2335</v>
+        <v>0.6222</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1653</v>
+        <v>0.1372</v>
       </c>
       <c r="G16" t="n">
         <v>0.0078</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3909</v>
+        <v>0.7516</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2335</v>
+        <v>0.6222</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1574</v>
+        <v>0.1294</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5764</v>
+        <v>0.6561</v>
       </c>
       <c r="E17" t="n">
         <v>-0.1864</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7628</v>
+        <v>0.8424</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7737000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1608</v>
+        <v>0.2405</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2568</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4176</v>
+        <v>0.4973</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3048</v>
+        <v>-1.6102</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06279999999999999</v>
+        <v>-1.2615</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3676</v>
+        <v>-0.3487</v>
       </c>
       <c r="G18" t="n">
         <v>-3.029</v>
@@ -1858,13 +1858,13 @@
         <v>2.5769</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3278</v>
+        <v>1.0224</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6154</v>
+        <v>0.2911</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7123</v>
+        <v>0.7313</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3274</v>
+        <v>-1.9094</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3207</v>
+        <v>-1.0151</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0067</v>
+        <v>-0.8944</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9235</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1968</v>
+        <v>0.2211</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.312</v>
+        <v>-0.0064</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1152</v>
+        <v>0.2275</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2071</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.76</v>
+        <v>-3.0808</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.2176</v>
+        <v>-3.8101</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4576</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5324</v>
@@ -2014,13 +2014,13 @@
         <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7635999999999999</v>
+        <v>1.4427</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5802</v>
+        <v>0.9877</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1834</v>
+        <v>0.4551</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6036</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7351</v>
+        <v>-3.8229</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.0896</v>
+        <v>-5.1727</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3544</v>
+        <v>1.3499</v>
       </c>
       <c r="G21" t="n">
         <v>-4.1916</v>
@@ -2092,13 +2092,13 @@
         <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3542</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9873</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6331</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0.6036</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.760400000000001</v>
+        <v>-7.7032</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.5979</v>
+        <v>-6.6811</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1625</v>
+        <v>-1.0221</v>
       </c>
       <c r="G22" t="n">
         <v>-8.1206</v>
@@ -2170,13 +2170,13 @@
         <v>1.9822</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2256</v>
+        <v>0.8316</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4844</v>
+        <v>0.4325</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2587</v>
+        <v>0.3991</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2071</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.716400000000001</v>
+        <v>-3.5158</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.750699999999998</v>
+        <v>-8.463799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>4.0342</v>
+        <v>4.947799999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-17.5687</v>
@@ -2248,13 +2248,13 @@
         <v>13.6774</v>
       </c>
       <c r="S23" t="n">
-        <v>8.281599999999999</v>
+        <v>8.482000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>4.7662</v>
+        <v>4.0532</v>
       </c>
       <c r="U23" t="n">
-        <v>3.515</v>
+        <v>4.4288</v>
       </c>
       <c r="V23" t="n">
         <v>5.768999999999998</v>
